--- a/astro-site/public/dl/hotel-checklist-templates/11-hotel-pool-checklists.xlsx
+++ b/astro-site/public/dl/hotel-checklist-templates/11-hotel-pool-checklists.xlsx
@@ -744,7 +744,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Measure free chlorine and pH and record them in the pool log: free chlorine at least 1.0 ppm (2.0 with CYA), pH 7.0–7.8, before opening and every 2 h (manual) or 4 h (automatic); keep records 3 years (MAHC 2024; your state or local code governs)</t>
+          <t>Measure free chlorine and pH and record them in the pool log: free chlorine at least 1.0 ppm (2.0 with CYA), pH 7.0–7.8, before opening and every 2 h (manual) or 4 h (automatic); if a reading is out of range, keep the pool closed until it is corrected; keep records 3 years (MAHC 2024; your state or local code governs)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
